--- a/data/lillestrom_monitoring_sites.xlsx
+++ b/data/lillestrom_monitoring_sites.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JES\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CFA8F5-2A71-4246-9938-1C08ED333E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134BFA3F-0D7A-48C7-8922-A968B86A9E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{9C3A7A90-CD7A-4778-99B7-8FCC1DE9F218}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{9C3A7A90-CD7A-4778-99B7-8FCC1DE9F218}"/>
   </bookViews>
   <sheets>
     <sheet name="catch_outlets" sheetId="2" r:id="rId1"/>
@@ -82,9 +82,6 @@
     <t>002-30586</t>
   </si>
   <si>
-    <t>Rud Nitelva (N8 )</t>
-  </si>
-  <si>
     <t>002-30578</t>
   </si>
   <si>
@@ -287,6 +284,9 @@
   </si>
   <si>
     <t>Not resolved by REGINE network</t>
+  </si>
+  <si>
+    <t>Rud Nitelva (N8)</t>
   </si>
 </sst>
 </file>
@@ -699,46 +699,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EDF06E-9BAB-44FC-82D2-D0BA4A260C8B}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.52734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.46875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.05859375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.64453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.41015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="50.3515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -753,15 +753,15 @@
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -776,18 +776,18 @@
         <v>484</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="7">
         <v>11.07367</v>
@@ -799,18 +799,18 @@
         <v>668</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="7">
         <v>11.20984</v>
@@ -822,18 +822,18 @@
         <v>212</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="7">
         <v>11.09281</v>
@@ -845,18 +845,18 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" s="7">
         <v>11.28279</v>
@@ -868,18 +868,18 @@
         <v>131</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7">
         <v>11.221299999999999</v>
@@ -891,7 +891,7 @@
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -903,19 +903,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4880EC8-8A50-4537-94A7-456C2129CA91}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.87890625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.41015625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.1171875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.29296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5859375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.5859375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.29296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -935,16 +935,16 @@
         <v>3</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -955,13 +955,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
         <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
       </c>
       <c r="G2" s="2">
         <v>11.01695</v>
@@ -970,10 +970,10 @@
         <v>59.958500000000001</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -984,13 +984,13 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
         <v>38</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
       </c>
       <c r="G3" s="2">
         <v>10.996169999999999</v>
@@ -999,10 +999,10 @@
         <v>59.944189999999999</v>
       </c>
       <c r="I3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1010,16 +1010,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
         <v>41</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
       </c>
       <c r="G4" s="2">
         <v>11.057</v>
@@ -1028,27 +1028,27 @@
         <v>59.945529999999998</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
         <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
       </c>
       <c r="G5" s="2">
         <v>11.0085</v>
@@ -1057,27 +1057,27 @@
         <v>59.97925</v>
       </c>
       <c r="I5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
         <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
       </c>
       <c r="G6" s="2">
         <v>11.10032</v>
@@ -1086,27 +1086,27 @@
         <v>59.950360000000003</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
         <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
       </c>
       <c r="G7" s="2">
         <v>11.08849</v>
@@ -1115,27 +1115,27 @@
         <v>59.997549999999997</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="2">
         <v>11.22099</v>
@@ -1144,27 +1144,27 @@
         <v>60.021630000000002</v>
       </c>
       <c r="I8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="2">
         <v>11.10637</v>
@@ -1173,27 +1173,27 @@
         <v>60.001989999999999</v>
       </c>
       <c r="I9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2">
         <v>11.300179999999999</v>
@@ -1202,27 +1202,27 @@
         <v>59.992089999999997</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
       <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>55</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
       </c>
       <c r="G11" s="2">
         <v>11.34807</v>
@@ -1231,27 +1231,27 @@
         <v>59.985120000000002</v>
       </c>
       <c r="I11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
         <v>57</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
       </c>
       <c r="G12" s="2">
         <v>11.348229999999999</v>
@@ -1260,27 +1260,27 @@
         <v>59.983910000000002</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
       <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
         <v>59</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
       </c>
       <c r="G13" s="2">
         <v>11.22275</v>
@@ -1289,7 +1289,7 @@
         <v>59.86139</v>
       </c>
       <c r="I13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
